--- a/docs/legal/review-2026-06-16/revised-lolo-care-inc/Legal/DRAFTS/Stocks/initial-cap-table-and-stock-ledger.xlsx
+++ b/docs/legal/review-2026-06-16/revised-lolo-care-inc/Legal/DRAFTS/Stocks/initial-cap-table-and-stock-ledger.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Charles Petrini Poli</t>
+          <t>Charles Petrini-Poli</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Charles Petrini Poli</t>
+          <t>Charles Petrini-Poli</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>$[CHARLES TOTAL PURCHASE PRICE]</t>
+          <t>$50.00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>$[THIBAUD TOTAL PURCHASE PRICE]</t>
+          <t>$30.00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
